--- a/Расчеты.xlsx
+++ b/Расчеты.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WPS\Этот сем\3DGraphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841D0EF9-23D5-46C2-9AFE-1FD29DBCFE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA61257-2FB5-41EA-8EF2-9BC3A76AE55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14889" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="20935" windowHeight="14889" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="2">
   <si>
     <t>X</t>
   </si>
@@ -141,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -159,9 +159,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -511,7 +508,7 @@
       <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="3">
@@ -526,7 +523,7 @@
       <c r="I2" s="3">
         <v>0</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="K2" s="3">
@@ -559,7 +556,7 @@
       <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="3">
         <v>0</v>
       </c>
@@ -572,7 +569,7 @@
       <c r="I3" s="3">
         <v>0</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="7"/>
       <c r="K3" s="3">
         <f>A3*F1+B3*F2+C3*F3+D3*F4</f>
         <v>0.1</v>
@@ -699,7 +696,7 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>0</v>
       </c>
       <c r="F7" s="3">
@@ -714,7 +711,7 @@
       <c r="I7" s="3">
         <v>0</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="9" t="s">
         <v>1</v>
       </c>
       <c r="K7" s="2"/>
@@ -727,7 +724,7 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="3">
         <v>0</v>
       </c>
@@ -740,7 +737,7 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="10"/>
+      <c r="J8" s="9"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -795,7 +792,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="2"/>
       <c r="F11" s="3">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
@@ -807,15 +804,15 @@
       <c r="J11" s="1"/>
       <c r="K11" s="3">
         <f>A11*F11+B11*F12+C11*F13+D11*F14</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3">
         <f>A11*G11+B11*G12+C11*G13+D11*G14</f>
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="M11" s="3">
         <f>A11*H11+B11*H12+C11*H13+D11*H14</f>
-        <v>0.89999999999999991</v>
+        <v>3</v>
       </c>
       <c r="N11" s="3"/>
     </row>
@@ -824,20 +821,20 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>0</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="9" t="s">
         <v>1</v>
       </c>
       <c r="K12" s="2"/>
@@ -850,7 +847,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="3">
         <v>0</v>
       </c>
@@ -858,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="3">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I13" s="3"/>
-      <c r="J13" s="10"/>
+      <c r="J13" s="9"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -900,71 +897,157 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="A16" s="3">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
+      <c r="I16" s="3">
+        <v>4</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="3">
+        <f>A16*F16+B16*F17+C16*F18+D16*F19</f>
+        <v>38</v>
+      </c>
+      <c r="L16" s="3">
+        <f>A16*G16+B16*G17+C16*G18+D16*G19</f>
+        <v>44</v>
+      </c>
+      <c r="M16" s="3">
+        <f>A16*H16+B16*H17+C16*H18+D16*H19</f>
+        <v>50</v>
+      </c>
+      <c r="N16" s="3">
+        <f>A16*I16+B16*I17+C16*I18+D16*I19</f>
+        <v>66</v>
+      </c>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="A17" s="3">
+        <v>1</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
+        <f>A17*I16+B17*I17+C17*I18+D17*I19</f>
+        <v>76</v>
+      </c>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="3">
+        <v>1</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3">
+        <v>30</v>
+      </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="F18" s="3">
+        <v>9</v>
+      </c>
+      <c r="G18" s="3">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3">
+        <v>11</v>
+      </c>
+      <c r="I18" s="3">
+        <v>12</v>
+      </c>
       <c r="J18" s="7"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
+        <f>A18*I16+B18*I17+C18*I18+D18*I19</f>
+        <v>86</v>
+      </c>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="A19" s="3">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -985,71 +1068,187 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="A21" s="3">
+        <v>1</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="3">
+        <f>A21*F21+B21*F22+C21*F23+D21*F24</f>
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <f>A21*G21+B21*G22+C21*G23+D21*G24</f>
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
+        <f>A21*H21+B21*H22+C21*H23+D21*H24</f>
+        <v>19</v>
+      </c>
+      <c r="N21" s="3">
+        <f>A21*I21+B21*I22+C21*I23+D21*I24</f>
+        <v>22</v>
+      </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+      <c r="A22" s="3">
+        <v>1</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3">
+        <f>A22*F21+B22*F22+C22*F23+D22*F24</f>
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <f>A22*G21+B22*G22+C22*G23+D22*G24</f>
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <f>A22*H21+B22*H22+C22*H23+D22*H24</f>
+        <v>29</v>
+      </c>
+      <c r="N22" s="3">
+        <f>A22*I21+B22*I22+C22*I23+D22*I24</f>
+        <v>32</v>
+      </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="A23" s="3">
+        <v>1</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
+        <v>30</v>
+      </c>
       <c r="E23" s="7"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4</v>
+      </c>
       <c r="J23" s="7"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+      <c r="K23" s="3">
+        <f>A23*F21+B23*F22+C23*F23+D23*F24</f>
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
+        <f>A23*G21+B23*G22+C23*G23+D23*G24</f>
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
+        <f>A23*H21+B23*H22+C23*H23+D23*H24</f>
+        <v>39</v>
+      </c>
+      <c r="N23" s="3">
+        <f>A23*I21+B23*I22+C23*I23+D23*I24</f>
+        <v>42</v>
+      </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="A24" s="3">
+        <v>0</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="3">
+        <f>A24*F21+B24*F22+C24*F23+D24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <f>A24*G21+B24*G22+C24*G23+D24*G24</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <f>A24*H21+B24*H22+C24*H23+D24*H24</f>
+        <v>1</v>
+      </c>
+      <c r="N24" s="3">
+        <f>A24*I21+B24*I22+C24*I23+D24*I24</f>
+        <v>1</v>
+      </c>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1180,7 +1379,11 @@
       <c r="L32" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="J17:J18"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="E7:E8"/>

--- a/Расчеты.xlsx
+++ b/Расчеты.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WPS\Этот сем\3DGraphics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA61257-2FB5-41EA-8EF2-9BC3A76AE55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB68CB5-2919-4A26-8A92-7114D9844C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="20935" windowHeight="14889" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14889" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="2">
   <si>
     <t>X</t>
   </si>
@@ -1069,16 +1069,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="3">
@@ -1096,34 +1096,28 @@
       <c r="J21" s="1"/>
       <c r="K21" s="3">
         <f>A21*F21+B21*F22+C21*F23+D21*F24</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <f>A21*G21+B21*G22+C21*G23+D21*G24</f>
-        <v>4</v>
+        <v>0.30886551699999998</v>
       </c>
       <c r="M21" s="3">
         <f>A21*H21+B21*H22+C21*H23+D21*H24</f>
-        <v>19</v>
+        <v>0.95110570000000005</v>
       </c>
       <c r="N21" s="3">
         <f>A21*I21+B21*I22+C21*I23+D21*I24</f>
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>1</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2</v>
-      </c>
-      <c r="C22" s="3">
-        <v>3</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>0</v>
@@ -1132,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>2</v>
+        <v>0.95110570000000005</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>-0.30886551699999998</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1143,79 +1137,49 @@
       <c r="J22" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K22" s="3">
-        <f>A22*F21+B22*F22+C22*F23+D22*F24</f>
-        <v>1</v>
-      </c>
-      <c r="L22" s="3">
-        <f>A22*G21+B22*G22+C22*G23+D22*G24</f>
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <f>A22*H21+B22*H22+C22*H23+D22*H24</f>
-        <v>29</v>
-      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
       <c r="N22" s="3">
         <f>A22*I21+B22*I22+C22*I23+D22*I24</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>1</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>0.30886551699999998</v>
       </c>
       <c r="H23" s="3">
-        <v>3</v>
+        <v>0.95110570000000005</v>
       </c>
       <c r="I23" s="3">
         <v>4</v>
       </c>
       <c r="J23" s="7"/>
-      <c r="K23" s="3">
-        <f>A23*F21+B23*F22+C23*F23+D23*F24</f>
-        <v>1</v>
-      </c>
-      <c r="L23" s="3">
-        <f>A23*G21+B23*G22+C23*G23+D23*G24</f>
-        <v>4</v>
-      </c>
-      <c r="M23" s="3">
-        <f>A23*H21+B23*H22+C23*H23+D23*H24</f>
-        <v>39</v>
-      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
       <c r="N23" s="3">
         <f>A23*I21+B23*I22+C23*I23+D23*I24</f>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-      <c r="C24" s="3">
-        <v>0</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
       <c r="D24" s="3">
         <v>1</v>
       </c>
@@ -1233,18 +1197,9 @@
         <v>1</v>
       </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="3">
-        <f>A24*F21+B24*F22+C24*F23+D24*F24</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <f>A24*G21+B24*G22+C24*G23+D24*G24</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <f>A24*H21+B24*H22+C24*H23+D24*H24</f>
-        <v>1</v>
-      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
       <c r="N24" s="3">
         <f>A24*I21+B24*I22+C24*I23+D24*I24</f>
         <v>1</v>
@@ -1269,71 +1224,142 @@
       <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+      <c r="A26" s="3">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="3">
+        <f>A26*F26+B26*F27+C26*F28+D26*F29</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <f>A26*G26+B26*G27+C26*G28+D26*G29</f>
+        <v>0.30886551699999998</v>
+      </c>
+      <c r="M26" s="3">
+        <f>A26*H26+B26*H27+C26*H28+D26*H29</f>
+        <v>0.95110570000000005</v>
+      </c>
+      <c r="N26" s="3">
+        <f>A26*I26+B26*I27+C26*I28+D26*I29</f>
+        <v>4</v>
+      </c>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0.95110570000000005</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-0.30886551699999998</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3">
+        <f>A27*I26+B27*I27+C27*I28+D27*I29</f>
+        <v>0</v>
+      </c>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0.30886551699999998</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.95110570000000005</v>
+      </c>
+      <c r="I28" s="3">
+        <v>4</v>
+      </c>
+      <c r="J28" s="7"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3">
+        <f>A28*I26+B28*I27+C28*I28+D28*I29</f>
+        <v>0</v>
+      </c>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3">
+        <f>A29*I26+B29*I27+C29*I28+D29*I29</f>
+        <v>1</v>
+      </c>
       <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -1379,7 +1405,9 @@
       <c r="L32" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="J27:J28"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="J22:J23"/>
     <mergeCell ref="E17:E18"/>
